--- a/行動予定表_1031.xlsx
+++ b/行動予定表_1031.xlsx
@@ -1152,7 +1152,7 @@
     <row r="19" ht="22.05" customHeight="1" s="29">
       <c r="A19" s="51" t="inlineStr">
         <is>
-          <t>14:00　謙二様邸（八千代市大和田950-8）資料お渡し　施工場所のお話し</t>
+          <t>14:00　謙二様邸（八千代市大和田950-8）市役所から届いた書類をお返しする　施工場所のお話し</t>
         </is>
       </c>
       <c r="B19" s="11" t="n"/>
@@ -1168,9 +1168,9 @@
       <c r="L19" s="12" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="29">
-      <c r="A20" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　渡す資料：【要記入】</t>
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　お返しする書類：市役所から届いた書類</t>
         </is>
       </c>
       <c r="B20" s="11" t="n"/>
